--- a/Excel Pruebas Calculadora de Liquidacion.xlsx
+++ b/Excel Pruebas Calculadora de Liquidacion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28417"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cesar\UDEM\Semestre 3\Codigo Limpio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Universidad\Codigisimo\Codigo Limpio\Calculadora-de-liquidaci-n-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF0F4EA5-D0C4-4FDA-BC0D-7ABFE9252EF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{615996EF-6917-4A79-BCFC-45D28F5B426E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{643A7808-E11E-40DC-9D1B-B90C41F0CEA7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{643A7808-E11E-40DC-9D1B-B90C41F0CEA7}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -110,12 +108,6 @@
     <t>Fechas ingresadas erroneamente</t>
   </si>
   <si>
-    <t>jueves, 31 de abril de 2026</t>
-  </si>
-  <si>
-    <t>ERROR: La fecha ingresada n</t>
-  </si>
-  <si>
     <t>Salario menor a SMMLV</t>
   </si>
   <si>
@@ -138,6 +130,12 @@
   </si>
   <si>
     <t>ERROR: Debe de ingresar números enteros en este apartado</t>
+  </si>
+  <si>
+    <t>ERROR: La fecha ingresada no existe</t>
+  </si>
+  <si>
+    <t>jueves, 32 de abril de 2026</t>
   </si>
 </sst>
 </file>
@@ -146,11 +144,11 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="166" formatCode="&quot;$&quot;\ #,##0"/>
-    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0;[Red]\-&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="168" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0;[Red]\-&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="167" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -216,17 +214,17 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -564,34 +562,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80557AFD-A4EB-4D8F-8841-C6D7F203AEC9}">
   <dimension ref="A1:K17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="37.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="11.08984375" customWidth="1"/>
-    <col min="7" max="7" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.36328125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="11.109375" customWidth="1"/>
+    <col min="7" max="7" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11">
       <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-    </row>
-    <row r="2" spans="1:11" ht="45.6" x14ac:dyDescent="0.3">
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+    </row>
+    <row r="2" spans="1:11" ht="45.75">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -623,17 +621,17 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="4">
         <v>1750905</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="7">
         <v>46023</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="7">
         <v>46387</v>
       </c>
       <c r="F3">
@@ -661,17 +659,17 @@
         <v>4587371.0999999996</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="4">
         <v>3501810</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="7">
         <v>46023</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="7">
         <v>46174</v>
       </c>
       <c r="F4">
@@ -699,17 +697,17 @@
         <v>3720673.125</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="4">
         <v>5050000</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="7">
         <v>46235</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="7">
         <v>46265</v>
       </c>
       <c r="F5">
@@ -737,30 +735,30 @@
         <v>1056291.6666666665</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11">
       <c r="B6" s="4"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-    </row>
-    <row r="7" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+    </row>
+    <row r="7" spans="1:11" ht="15.75">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="4"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" t="s">
         <v>17</v>
       </c>
       <c r="B8" s="4">
         <v>6000000</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="7">
         <v>46032</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="7">
         <v>46042</v>
       </c>
       <c r="F8">
@@ -788,17 +786,17 @@
         <v>417222.22222222225</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11">
       <c r="A9" t="s">
         <v>22</v>
       </c>
       <c r="B9" s="4">
         <v>1750905</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="7">
         <v>46174</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="7">
         <v>46235</v>
       </c>
       <c r="F9">
@@ -826,17 +824,17 @@
         <v>735380.1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B10" s="4">
         <v>1600000</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="7">
         <v>46271</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="7">
         <v>46326</v>
       </c>
       <c r="F10">
@@ -864,36 +862,36 @@
         <v>615592.59259259258</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11">
       <c r="B11" s="4"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
     </row>
-    <row r="12" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="15.75">
       <c r="A12" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="4"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11">
       <c r="A13" t="s">
         <v>18</v>
       </c>
       <c r="B13" s="4">
         <v>0</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="7">
         <v>46178</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="7">
         <v>46172</v>
       </c>
       <c r="F13" s="3" t="s">
@@ -902,17 +900,17 @@
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11">
       <c r="A14" t="s">
         <v>20</v>
       </c>
       <c r="B14" s="4">
         <v>1750905</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="7">
         <v>46122</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="7">
         <v>46109</v>
       </c>
       <c r="F14" s="3" t="s">
@@ -921,59 +919,59 @@
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11">
       <c r="A15" t="s">
         <v>23</v>
       </c>
       <c r="B15" s="4">
         <v>5252715</v>
       </c>
-      <c r="C15" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" s="8">
+      <c r="C15" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="7">
         <v>46143</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B16" s="4">
         <v>3500000</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>29</v>
       </c>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="7">
+        <v>46204</v>
+      </c>
+      <c r="D17" s="7">
+        <v>46242</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C17" s="8">
-        <v>46204</v>
-      </c>
-      <c r="D17" s="8">
-        <v>46242</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>33</v>
       </c>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
